--- a/data/trans_orig/Q64C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q64C-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que trabaja a la semana</t>
+          <t>Número medio de horas que trabaja a la semana (tasa de respuesta: 97,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,66; 42,97</t>
+          <t>40,69; 42,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,4; 45,63</t>
+          <t>42,45; 45,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,45; 44,06</t>
+          <t>39,57; 43,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,48; 41,12</t>
+          <t>37,59; 41,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,42; 41,19</t>
+          <t>35,6; 40,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,7; 38,55</t>
+          <t>34,05; 38,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,47; 39,36</t>
+          <t>33,64; 39,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,19; 33,53</t>
+          <t>26,17; 33,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,7; 41,81</t>
+          <t>39,73; 41,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,1; 41,89</t>
+          <t>39,14; 41,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,24; 41,76</t>
+          <t>38,32; 41,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,86; 38,0</t>
+          <t>33,68; 37,72</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,24; 42,43</t>
+          <t>41,25; 42,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,76; 41,96</t>
+          <t>40,69; 41,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,21; 40,54</t>
+          <t>39,23; 40,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,47; 40,57</t>
+          <t>21,85; 40,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,24; 38,23</t>
+          <t>36,17; 38,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,98; 37,04</t>
+          <t>34,81; 36,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,37; 36,32</t>
+          <t>34,44; 36,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,57; 36,23</t>
+          <t>31,54; 36,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,69; 40,76</t>
+          <t>39,69; 40,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38,73; 39,8</t>
+          <t>38,68; 39,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37,5; 38,66</t>
+          <t>37,42; 38,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,07; 38,26</t>
+          <t>25,59; 38,37</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,7; 39,56</t>
+          <t>37,61; 39,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,38; 40,62</t>
+          <t>38,39; 40,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,11; 38,35</t>
+          <t>35,99; 38,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,1; 39,05</t>
+          <t>37,18; 39,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,42; 37,43</t>
+          <t>35,4; 37,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,23; 36,73</t>
+          <t>34,27; 36,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,35; 34,92</t>
+          <t>32,36; 34,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,86; 36,56</t>
+          <t>34,93; 36,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,95; 38,32</t>
+          <t>36,93; 38,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,88; 38,66</t>
+          <t>36,94; 38,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,62; 36,33</t>
+          <t>34,72; 36,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,37; 37,57</t>
+          <t>36,31; 37,56</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,69; 41,6</t>
+          <t>40,71; 41,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,74; 41,76</t>
+          <t>40,74; 41,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,9; 40,01</t>
+          <t>38,84; 39,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,74; 39,93</t>
+          <t>25,19; 39,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,34; 37,83</t>
+          <t>36,41; 37,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,12; 36,64</t>
+          <t>35,03; 36,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,17; 35,68</t>
+          <t>34,13; 35,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,16; 35,86</t>
+          <t>32,53; 35,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,36; 40,13</t>
+          <t>39,34; 40,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38,64; 39,51</t>
+          <t>38,62; 39,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,04; 37,97</t>
+          <t>37,05; 37,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,27; 37,72</t>
+          <t>29,22; 37,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q64C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q64C-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39,42</t>
+          <t>39,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30,77</t>
+          <t>32,71</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,26</t>
+          <t>37,19</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,69; 42,82</t>
+          <t>40,82; 42,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,45; 45,72</t>
+          <t>42,33; 45,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,57; 43,92</t>
+          <t>39,94; 43,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,59; 41,0</t>
+          <t>37,78; 41,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,6; 40,78</t>
+          <t>35,65; 41,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,05; 38,66</t>
+          <t>34,06; 38,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,64; 39,59</t>
+          <t>33,49; 39,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,17; 33,77</t>
+          <t>29,83; 35,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,73; 41,93</t>
+          <t>39,66; 41,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,14; 41,95</t>
+          <t>39,11; 41,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,32; 41,89</t>
+          <t>38,25; 41,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,68; 37,72</t>
+          <t>35,76; 38,59</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34,56</t>
+          <t>40,59</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,8</t>
+          <t>35,7</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34,66</t>
+          <t>38,51</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,25; 42,52</t>
+          <t>41,22; 42,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,69; 41,98</t>
+          <t>40,69; 41,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,23; 40,6</t>
+          <t>39,2; 40,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,85; 40,58</t>
+          <t>40,09; 41,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,17; 38,15</t>
+          <t>36,27; 38,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,81; 36,89</t>
+          <t>34,87; 36,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,44; 36,33</t>
+          <t>34,39; 36,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,54; 36,22</t>
+          <t>35,06; 36,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,69; 40,74</t>
+          <t>39,72; 40,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38,68; 39,79</t>
+          <t>38,73; 39,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37,42; 38,61</t>
+          <t>37,46; 38,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,59; 38,37</t>
+          <t>38,12; 38,92</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38,17</t>
+          <t>38,12</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35,73</t>
+          <t>35,52</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,95</t>
+          <t>36,82</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,61; 39,42</t>
+          <t>37,68; 39,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,39; 40,63</t>
+          <t>38,41; 40,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,99; 38,26</t>
+          <t>36,05; 38,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,18; 39,06</t>
+          <t>37,2; 38,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,4; 37,38</t>
+          <t>35,49; 37,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,27; 36,63</t>
+          <t>34,39; 36,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,36; 34,88</t>
+          <t>32,27; 34,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,93; 36,47</t>
+          <t>34,69; 36,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,93; 38,36</t>
+          <t>36,94; 38,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,94; 38,61</t>
+          <t>37,03; 38,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,72; 36,33</t>
+          <t>34,65; 36,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,31; 37,56</t>
+          <t>36,2; 37,36</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35,71</t>
+          <t>39,87</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,88</t>
+          <t>35,48</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,35</t>
+          <t>37,93</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,71; 41,65</t>
+          <t>40,67; 41,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,74; 41,81</t>
+          <t>40,78; 41,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,84; 39,98</t>
+          <t>38,83; 40,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,19; 39,88</t>
+          <t>39,39; 40,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,41; 37,96</t>
+          <t>36,34; 37,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,03; 36,63</t>
+          <t>35,14; 36,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,13; 35,7</t>
+          <t>34,12; 35,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,53; 35,8</t>
+          <t>35,05; 35,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,34; 40,16</t>
+          <t>39,34; 40,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38,62; 39,51</t>
+          <t>38,59; 39,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,05; 37,96</t>
+          <t>37,06; 37,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,22; 37,72</t>
+          <t>37,61; 38,27</t>
         </is>
       </c>
     </row>
